--- a/file_upload_forms/037_drop_close_submission_form--file_upload_forms.xlsx
+++ b/file_upload_forms/037_drop_close_submission_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>drop_close_submission_form_page_1</t>
+          <t>upload_evidence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>upload_evidence</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Upload Evidence</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please upload relevant evidence for this submission</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,38 +547,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>close_details</t>
+          <t>upload_evidence_page_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>details</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Evidence Description</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Briefly describe the uploaded evidence</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>closure_date</t>
+          <t>facility_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>closure_date</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select facility related to this submission</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -584,20 +596,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>closure_time</t>
+          <t>facility_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>closure_time</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Facility Details</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select additional facility information</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>facility_id</t>
+          <t>operation_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>facility</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Operation</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select operation related to this submission</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>facility_id_2</t>
+          <t>operation_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>facility_name</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Operation Details</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select additional operation information</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>operation_id</t>
+          <t>logistics_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>operation</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Logistics</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select logistics information</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>operation_id_2</t>
+          <t>logistics_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>operation_name</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Logistics Details</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select additional logistics information</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>logistics_id</t>
+          <t>team_leader_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>logistics</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Team Leader</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select team leader</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>logistics_id_2</t>
+          <t>team_leader_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>logistics_name</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Team Leader Details</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select additional team leader information</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -745,66 +785,78 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>team_leader_id</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>team_leader</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Provide any additional comments</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>team_leader_id_2</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>team_leader_name</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Closure Date</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select closure date</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>upload_file</t>
+          <t>submission_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>upload_file</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Closure Time</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Select closure time</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,18 +871,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Submit</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Submit this form</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submit</t>
+          <t>upload_file</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Upload File</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Upload relevant file</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -860,20 +920,24 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>upload_file_2</t>
+          <t>facility_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>upload_file_2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Facility 3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Select facility</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -883,20 +947,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>comments_2</t>
+          <t>facility_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>comments_2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>Facility 4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Select additional facility information</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -906,182 +974,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>facility_id_3</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>facility</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Comments 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Provide any additional comments</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>facility_id_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>facility_name</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>operation_id_3</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>operation_id_4</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>operation_name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>logistics_id_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>logistics</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>logistics_id_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>logistics_name</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>team_leader_id_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>team_leader</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>team_leader_id_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>team_leader_name</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,544 +1037,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>facility_id_choices</t>
+          <t>facility_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>facility_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Facility A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>facility_id_choices</t>
+          <t>facility_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>facility_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Facility B</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>facility_id_2_choices</t>
+          <t>facility_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>facility_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Facility C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>facility_id_2_choices</t>
+          <t>facility_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>facility_d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Facility D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>operation_id_choices</t>
+          <t>operation_1_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>operation_e</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Operation E</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>operation_id_choices</t>
+          <t>operation_1_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>operation_f</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Operation F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>operation_id_2_choices</t>
+          <t>operation_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>operation_g</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Operation G</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>operation_id_2_choices</t>
+          <t>operation_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>operation_h</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Operation H</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>logistics_id_choices</t>
+          <t>logistics_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>logistics_i</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Logistics I</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>logistics_id_choices</t>
+          <t>logistics_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>logistics_j</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Logistics J</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>logistics_id_2_choices</t>
+          <t>logistics_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>logistics_k</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Logistics K</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>logistics_id_2_choices</t>
+          <t>logistics_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>logistics_l</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Logistics L</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>team_leader_id_choices</t>
+          <t>team_leader_1_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>team_leader_m</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Team Leader M</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>team_leader_id_choices</t>
+          <t>team_leader_1_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>team_leader_n</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Team Leader N</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>team_leader_id_2_choices</t>
+          <t>team_leader_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>team_leader_o</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Team Leader O</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>team_leader_id_2_choices</t>
+          <t>team_leader_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>team_leader_p</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Team Leader P</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>facility_id_3_choices</t>
+          <t>facility_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>facility_q</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Facility Q</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>facility_id_3_choices</t>
+          <t>facility_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>facility_r</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Facility R</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>facility_id_4_choices</t>
+          <t>facility_4_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>facility_s</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Facility S</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>facility_id_4_choices</t>
+          <t>facility_4_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>facility_t</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>operation_id_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>operation_id_3_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>operation_id_4_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>operation_id_4_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>logistics_id_2_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>logistics_id_2_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>logistics_id_3_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>logistics_id_3_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>team_leader_id_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>team_leader_id_2_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>team_leader_id_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>team_leader_id_3_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Facility T</t>
         </is>
       </c>
     </row>
